--- a/vault-dalarna-university/01 IIT/Analys/Innehåll.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Innehåll.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Innehåll" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1984,7 +1984,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (692 tecken): Kursen är en introduktiontill matematikdidaktik som vetenskapsområde och undervisningspraktik. I kursen behandlas olika …</t>
+          <t>Osannolikt kort (32 tecken): 'Kursen består av fyra delkurser.'</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1093 tecken): Kursen belyser matematikens historia i stora drag, med särskild tonvikt på olika talsystem, symboler och räkneoperatione…</t>
+          <t>5 meningar i ett stycke (692 tecken): Kursen är en introduktiontill matematikdidaktik som vetenskapsområde och undervisningspraktik. I kursen behandlas olika …</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (643 tecken): I kursen introduceras nationell såväl som internationell forskning om hur elever lär matematik och hur undervisningen ka…</t>
+          <t>8 meningar i ett stycke (1093 tecken): Kursen belyser matematikens historia i stora drag, med särskild tonvikt på olika talsystem, symboler och räkneoperatione…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (610 tecken): I kursen introduceras nationell såväl som internationell forskning om hur elever lär matematik och hur undervisningen ka…</t>
+          <t>4 meningar i ett stycke (643 tecken): I kursen introduceras nationell såväl som internationell forskning om hur elever lär matematik och hur undervisningen ka…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (513 tecken): I kursen behandlas grundläggande diskret matematik. Områden som diskuteras, analyseras och tillämpas är aritmetik, mängd…</t>
+          <t>4 meningar i ett stycke (610 tecken): I kursen introduceras nationell såväl som internationell forskning om hur elever lär matematik och hur undervisningen ka…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (468 tecken): Studenten arbetar under kursens gång med ett projekt som syftar till att förbättra någon egenskap eller att ta fram ett …</t>
+          <t>4 meningar i ett stycke (513 tecken): I kursen behandlas grundläggande diskret matematik. Områden som diskuteras, analyseras och tillämpas är aritmetik, mängd…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (650 tecken): Studenten arbetar självständigt med problemlösning inom ett maskintekniskt område. Studenten söker själv upp ett lämplig…</t>
+          <t>4 meningar i ett stycke (468 tecken): Studenten arbetar under kursens gång med ett projekt som syftar till att förbättra någon egenskap eller att ta fram ett …</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (424 tecken): Grundläggande teori och begrepp inom FEM introduceras. FEM modellens approximativa karaktär och dess inverkan på resulta…</t>
+          <t>7 meningar i ett stycke (650 tecken): Studenten arbetar självständigt med problemlösning inom ett maskintekniskt område. Studenten söker själv upp ett lämplig…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GMT338</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (574 tecken): Kursen inleds med en grundläggande genomgång av tillämpningsområden för CAD som konstruktionsverktyg varefter grunderna …</t>
+          <t>6 meningar i ett stycke (424 tecken): Grundläggande teori och begrepp inom FEM introduceras. FEM modellens approximativa karaktär och dess inverkan på resulta…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMT338</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (737 tecken): Kursen behandlar de vanligaste verkstadstekniska bearbetningsmetoderna ur ett produktionstekniskt perspektiv, dvs den pr…</t>
+          <t>5 meningar i ett stycke (574 tecken): Kursen inleds med en grundläggande genomgång av tillämpningsområden för CAD som konstruktionsverktyg varefter grunderna …</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (627 tecken): Kursen inleds med en genomgång av olika industrirobotars uppbyggnad och dess för- och nackdelar. Termer och vanliga begr…</t>
+          <t>4 meningar i ett stycke (737 tecken): Kursen behandlar de vanligaste verkstadstekniska bearbetningsmetoderna ur ett produktionstekniskt perspektiv, dvs den pr…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GMT34P</t>
+          <t>GMT34K</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (662 tecken): Kursen behandlar programmering av Computerized Numerical Control (CNC)-styrda verktygsmaskiner. Inledningsvis diskuteras…</t>
+          <t>7 meningar i ett stycke (627 tecken): Kursen inleds med en genomgång av olika industrirobotars uppbyggnad och dess för- och nackdelar. Termer och vanliga begr…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMT34Q</t>
+          <t>GMT34P</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (725 tecken): Kursen behandlar de grundläggande principerna och praxis för hållbar tillverkning. Vidare behandlas tillverkningens påve…</t>
+          <t>5 meningar i ett stycke (662 tecken): Kursen behandlar programmering av Computerized Numerical Control (CNC)-styrda verktygsmaskiner. Inledningsvis diskuteras…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34P</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GMT34W</t>
+          <t>GMT34Q</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (559 tecken): I kursen skall studenten självständigt utforma ett examensarbete inom ett avgränsat område inom maskinteknik. Uppgiften …</t>
+          <t>4 meningar i ett stycke (725 tecken): Kursen behandlar de grundläggande principerna och praxis för hållbar tillverkning. Vidare behandlas tillverkningens påve…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34Q</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMT34W</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (415 tecken): Kursen avhandlar på en grundläggande nivå grundbegreppen spänning och töjning. Enklare stångsystem avhandlas och definit…</t>
+          <t>5 meningar i ett stycke (559 tecken): I kursen skall studenten självständigt utforma ett examensarbete inom ett avgränsat område inom maskinteknik. Uppgiften …</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34W</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (702 tecken): Kursen behandlar olika halvledarmaterial och deras lämplighet för solcellstillverkning, absorbtion av solstrålningen i h…</t>
+          <t>6 meningar i ett stycke (415 tecken): Kursen avhandlar på en grundläggande nivå grundbegreppen spänning och töjning. Enklare stångsystem avhandlas och definit…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (479 tecken): Kursen behandlar elgenerering med solceller i nätanslutna och fristående system samt i hybridsystem där andra typer av g…</t>
+          <t>6 meningar i ett stycke (702 tecken): Kursen behandlar olika halvledarmaterial och deras lämplighet för solcellstillverkning, absorbtion av solstrålningen i h…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AEG294</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (597 tecken): Kursen täcker fyra aspekter av energipositiva stadsdelar. Den första aspekten är definitionen och sammanhanget av energi…</t>
+          <t>4 meningar i ett stycke (479 tecken): Kursen behandlar elgenerering med solceller i nätanslutna och fristående system samt i hybridsystem där andra typer av g…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>AEG294</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (460 tecken): Kursen behandlar elgenerering med solceller i nätanslutna system. Kursen börjar med en genomgång av de vanligaste kompon…</t>
+          <t>6 meningar i ett stycke (597 tecken): Kursen täcker fyra aspekter av energipositiva stadsdelar. Den första aspekten är definitionen och sammanhanget av energi…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AEG2AT</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (437 tecken): Kursen behandlar elgenerering med solceller i nätanslutna system. Kursen inleds med en översikt över elnätets uppbyggnad…</t>
+          <t>5 meningar i ett stycke (460 tecken): Kursen behandlar elgenerering med solceller i nätanslutna system. Kursen börjar med en genomgång av de vanligaste kompon…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AEG2AW</t>
+          <t>AEG2AT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (671 tecken): Kursen täcker fyra aspekter av urbana energisystem. Den första aspekten är definitionen och sammanhanget av urbana energ…</t>
+          <t>4 meningar i ett stycke (437 tecken): Kursen behandlar elgenerering med solceller i nätanslutna system. Kursen inleds med en översikt över elnätets uppbyggnad…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AEG2AY</t>
+          <t>AEG2AW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (703 tecken): Kursen behandlar elektriska lagringssystem och tjänster dessa system kan tillhandahålla. I kursen ligger fokus på batter…</t>
+          <t>7 meningar i ett stycke (671 tecken): Kursen täcker fyra aspekter av urbana energisystem. Den första aspekten är definitionen och sammanhanget av urbana energ…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>AEG2AY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (570 tecken): I kursen behandlas solstrålningens fysik, geometri, tillgänglighet i tid och rum, olika sätt att mäta solstrålning, samt…</t>
+          <t>6 meningar i ett stycke (703 tecken): Kursen behandlar elektriska lagringssystem och tjänster dessa system kan tillhandahålla. I kursen ligger fokus på batter…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AEG2C4</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (528 tecken): Kursens fokus är på design av fristående och hybrida solcellssystem, vilket inkluderar andra typer av elgeneratorer. Kur…</t>
+          <t>4 meningar i ett stycke (570 tecken): I kursen behandlas solstrålningens fysik, geometri, tillgänglighet i tid och rum, olika sätt att mäta solstrålning, samt…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>BEG222</t>
+          <t>AEG2C4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (453 tecken): I kursen diskuteras forskning, forskningsmetodik, presentationsteknik och hur man kan pröva och utveckla idéer. Studente…</t>
+          <t>4 meningar i ett stycke (528 tecken): Kursens fokus är på design av fristående och hybrida solcellssystem, vilket inkluderar andra typer av elgeneratorer. Kur…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>EG1012</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (445 tecken): Kursen omfattar totalt tre delar. Den första delen är grunden för strömningslära, inklusive egenskaper av vätskor, stabi…</t>
+          <t>4 meningar i ett stycke (453 tecken): I kursen diskuteras forskning, forskningsmetodik, presentationsteknik och hur man kan pröva och utveckla idéer. Studente…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (861 tecken): Kursen inleds med en genomgång av olika tekniker för att generera el och alstra värme ur förnybara resurser i hållbara e…</t>
+          <t>4 meningar i ett stycke (445 tecken): Kursen omfattar totalt tre delar. Den första delen är grunden för strömningslära, inklusive egenskaper av vätskor, stabi…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1481 tecken): Kursen börjar med en översikt över olika sätt att utforma en byggnad för att reducera byggnaders behov av energi för upp…</t>
+          <t>6 meningar i ett stycke (861 tecken): Kursen inleds med en genomgång av olika tekniker för att generera el och alstra värme ur förnybara resurser i hållbara e…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (664 tecken): I kursen behandlas solstrålningens fysik, geometri, tillgänglighet i tid och rum, olika sätt att mäta solstrålning, samt…</t>
+          <t>7 meningar i ett stycke (1481 tecken): Kursen börjar med en översikt över olika sätt att utforma en byggnad för att reducera byggnaders behov av energi för upp…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (564 tecken): Studenten ska ges möjlighet att använda sina teoretiska kunskaper inom solenenergiteknik i praktisk yrkesverksamhet. Stu…</t>
+          <t>4 meningar i ett stycke (664 tecken): I kursen behandlas solstrålningens fysik, geometri, tillgänglighet i tid och rum, olika sätt att mäta solstrålning, samt…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (565 tecken): Studenten ska ges möjlighet att använda sina teoretiska kunskaper inom solenenergiteknik i praktisk yrkesverksamhet. Stu…</t>
+          <t>4 meningar i ett stycke (564 tecken): Studenten ska ges möjlighet att använda sina teoretiska kunskaper inom solenenergiteknik i praktisk yrkesverksamhet. Stu…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (795 tecken): Examensarbetet är ett självständigt arbete som bygger på kunskaper förvärvade under utbildningen. Med självständigt arbe…</t>
+          <t>5 meningar i ett stycke (565 tecken): Studenten ska ges möjlighet att använda sina teoretiska kunskaper inom solenenergiteknik i praktisk yrkesverksamhet. Stu…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (786 tecken): Examensarbetet är ett självständigt arbete, som bygger på tidigare förvärvade kunskaper. Med självständigt arbete menas …</t>
+          <t>8 meningar i ett stycke (795 tecken): Examensarbetet är ett självständigt arbete som bygger på kunskaper förvärvade under utbildningen. Med självständigt arbe…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (987 tecken): Examensarbetet är ett självständigt ingenjörsmässigt arbete, som bygger på kunskaper förvärvade under utbildningen. Med …</t>
+          <t>8 meningar i ett stycke (786 tecken): Examensarbetet är ett självständigt arbete, som bygger på tidigare förvärvade kunskaper. Med självständigt arbete menas …</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (500 tecken): Kursen behandlar solvärmeteknikens grundläggande begrepp samt solvärmens funktion och möjligheter i ett värmesystem. Frå…</t>
+          <t>9 meningar i ett stycke (987 tecken): Examensarbetet är ett självständigt ingenjörsmässigt arbete, som bygger på kunskaper förvärvade under utbildningen. Med …</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GEG2UL</t>
+          <t>GEG2JP</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (926 tecken): Kursen behandlar teoretiska grunder, anläggningar och del/hjälpsystem för kraftgenerering ur vanligt förekommande förnyb…</t>
+          <t>5 meningar i ett stycke (500 tecken): Kursen behandlar solvärmeteknikens grundläggande begrepp samt solvärmens funktion och möjligheter i ett värmesystem. Frå…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (400 tecken): Kursen behandlar solstrålningens potential och fördelning över tid och beroende på det geografiska läget. Kursen innehål…</t>
+          <t>5 meningar i ett stycke (926 tecken): Kursen behandlar teoretiska grunder, anläggningar och del/hjälpsystem för kraftgenerering ur vanligt förekommande förnyb…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GEG33B</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (455 tecken): Kursen behandlar dimensionering, montage,installation och driftsättning av solcellssystem samt drift och underhåll med d…</t>
+          <t>4 meningar i ett stycke (400 tecken): Kursen behandlar solstrålningens potential och fördelning över tid och beroende på det geografiska läget. Kursen innehål…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GEG38F</t>
+          <t>GEG33B</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (709 tecken): I kursen behandlas teorin bakom, samt tillämpningar inom, grundläggande termodynamik, strömnings- samt värmelära, där en…</t>
+          <t>5 meningar i ett stycke (455 tecken): Kursen behandlar dimensionering, montage,installation och driftsättning av solcellssystem samt drift och underhåll med d…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GEG3A2</t>
+          <t>GEG38F</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (631 tecken): Kursen inleds med en introduktion om solstrålningens fysik och potential, fördelning över tid samt beroende av geografi.…</t>
+          <t>5 meningar i ett stycke (709 tecken): I kursen behandlas teorin bakom, samt tillämpningar inom, grundläggande termodynamik, strömnings- samt värmelära, där en…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GEG3BX</t>
+          <t>GEG3A2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (677 tecken): Kursen behandlar system för elektromagnetisk energiomvandling bestående av elektriska maskiner och drivsystem. Vidare be…</t>
+          <t>5 meningar i ett stycke (631 tecken): Kursen inleds med en introduktion om solstrålningens fysik och potential, fördelning över tid samt beroende av geografi.…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3BX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3A2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>GEG3BX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (492 tecken): Kursen behandlar befolknings- och sociala förändringars påverkan på samhällsutvecklingen. Kursen behandlar grundläggande…</t>
+          <t>5 meningar i ett stycke (677 tecken): Kursen behandlar system för elektromagnetisk energiomvandling bestående av elektriska maskiner och drivsystem. Vidare be…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3BX</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (744 tecken): Kursen innebär fördjupning inom planeringens teoribildningar för några valbara kunskapsfält samt tekniker för och prakti…</t>
+          <t>4 meningar i ett stycke (492 tecken): Kursen behandlar befolknings- och sociala förändringars påverkan på samhällsutvecklingen. Kursen behandlar grundläggande…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (464 tecken): Kursen behandlar form- och gestaltningskoncept och övar studentens förmåga att strukturera idéer och tänka kritiskt krin…</t>
+          <t>5 meningar i ett stycke (744 tecken): Kursen innebär fördjupning inom planeringens teoribildningar för några valbara kunskapsfält samt tekniker för och prakti…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSQ25J</t>
+          <t>GSQ25F</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (724 tecken): Kursen behandlar kvalitativa metoder, med inriktning dels mot specifika egenskaper och användningsområden för olika meto…</t>
+          <t>4 meningar i ett stycke (464 tecken): Kursen behandlar form- och gestaltningskoncept och övar studentens förmåga att strukturera idéer och tänka kritiskt krin…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1432 tecken): Kursen ger en överblick över städer som företeelse i ett historiskt utvecklingsperspektiv och urbangeografiska koncept f…</t>
+          <t>5 meningar i ett stycke (724 tecken): Kursen behandlar kvalitativa metoder, med inriktning dels mot specifika egenskaper och användningsområden för olika meto…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GSQ25N</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (825 tecken): I examensarbetet ska studenterna visa att de självständigt kan identifiera en problemställning inom ämnesområdet samt pl…</t>
+          <t>8 meningar i ett stycke (1432 tecken): Kursen ger en överblick över städer som företeelse i ett historiskt utvecklingsperspektiv och urbangeografiska koncept f…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSQ2DH</t>
+          <t>GSQ25N</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (629 tecken): Kursen inleds med att studenterna skapar tematiska kartor i GIS med stöd i kurslitteraturens beskrivning av rådande konv…</t>
+          <t>6 meningar i ett stycke (825 tecken): I examensarbetet ska studenterna visa att de självständigt kan identifiera en problemställning inom ämnesområdet samt pl…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSQ2H7</t>
+          <t>GSQ2DH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (924 tecken): Kursen behandlar den nationella arkitektur-, form- och designpolitiken, dess förankring i hållbarhetsmål och hur den öve…</t>
+          <t>5 meningar i ett stycke (629 tecken): Kursen inleds med att studenterna skapar tematiska kartor i GIS med stöd i kurslitteraturens beskrivning av rådande konv…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GSQ2H7</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1016 tecken): Kursen behandlar den översiktliga planeringens former i Sverige. Viktiga planeringsdokument och lagar som styr det övers…</t>
+          <t>6 meningar i ett stycke (924 tecken): Kursen behandlar den nationella arkitektur-, form- och designpolitiken, dess förankring i hållbarhetsmål och hur den öve…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L9</t>
+          <t>GSQ2L8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (465 tecken): Kursen inleds med att grundläggande färdigheter i GIS lärs ut. Studenterna skapar tematiska kartor i GIS med stöd i kurs…</t>
+          <t>7 meningar i ett stycke (1016 tecken): Kursen behandlar den översiktliga planeringens former i Sverige. Viktiga planeringsdokument och lagar som styr det övers…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GSQ2L9</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (479 tecken): Kursen ger studenten en orientering inom trafik- och transportområdet. Bland annat behandlas frågor såsom hur trafik och…</t>
+          <t>4 meningar i ett stycke (465 tecken): Kursen inleds med att grundläggande färdigheter i GIS lärs ut. Studenterna skapar tematiska kartor i GIS med stöd i kurs…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSQ2R5</t>
+          <t>GSQ2MC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (422 tecken): Kursen behandlar olika kvantitativa angreppssätt på hur den byggda miljön kan beskrivas och analyseras ur ett urbant- oc…</t>
+          <t>4 meningar i ett stycke (479 tecken): Kursen ger studenten en orientering inom trafik- och transportområdet. Bland annat behandlas frågor såsom hur trafik och…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>GSQ2R5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (479 tecken): Kursen behandlar befolknings- och sociala förändringars påverkan på samhällsutvecklingen. Kursen behandlar begrepp samt …</t>
+          <t>4 meningar i ett stycke (422 tecken): Kursen behandlar olika kvantitativa angreppssätt på hur den byggda miljön kan beskrivas och analyseras ur ett urbant- oc…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>GSQ2VY</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (472 tecken): Kursen inleds med att grundläggande färdigheter i geografiska informationssystem, GIS lärs ut. Studenterna skapar temati…</t>
+          <t>4 meningar i ett stycke (479 tecken): Kursen behandlar befolknings- och sociala förändringars påverkan på samhällsutvecklingen. Kursen behandlar begrepp samt …</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSQ2Y2</t>
+          <t>GSQ2WM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (489 tecken): Kursen behandlar kvalitativa metoders specifika egenskaper och användningsområden samt olika analysmetoder och färdighet…</t>
+          <t>4 meningar i ett stycke (472 tecken): Kursen inleds med att grundläggande färdigheter i geografiska informationssystem, GIS lärs ut. Studenterna skapar temati…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSQ33M</t>
+          <t>GSQ2Y2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (744 tecken): Kursen innebär fördjupning inom planeringens teoribildningar för några valbara kunskapsfält samt tekniker för och prakti…</t>
+          <t>4 meningar i ett stycke (489 tecken): Kursen behandlar kvalitativa metoders specifika egenskaper och användningsområden samt olika analysmetoder och färdighet…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GSQ33M</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (1432 tecken): Kursen ger en överblick över städer som företeelse i ett historiskt utvecklingsperspektiv och urbangeografiska koncept f…</t>
+          <t>5 meningar i ett stycke (744 tecken): Kursen innebär fördjupning inom planeringens teoribildningar för några valbara kunskapsfält samt tekniker för och prakti…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33M</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SQ1003</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (724 tecken): Kursen behandlar kvalitativa metoder, med inriktning dels mot specifika egenskaper och användningsområden för olika meto…</t>
+          <t>8 meningar i ett stycke (1432 tecken): Kursen ger en överblick över städer som företeelse i ett historiskt utvecklingsperspektiv och urbangeografiska koncept f…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>SQ1003</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (941 tecken): Kursen tar upp hur man sammanfattar data med centralmått, spridningsmått och sambandsmått och hur data analyseras med hj…</t>
+          <t>5 meningar i ett stycke (724 tecken): Kursen behandlar kvalitativa metoder, med inriktning dels mot specifika egenskaper och användningsområden för olika meto…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>GST2CL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1211 tecken): I kursen ingår att hitta offentlig statistik samt att beskriva data med hjälp av olika grafer och att dra slutsatser om …</t>
+          <t>8 meningar i ett stycke (941 tecken): Kursen tar upp hur man sammanfattar data med centralmått, spridningsmått och sambandsmått och hur data analyseras med hj…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>ST1013</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (872 tecken): Kursen fokuserar främst på de tillämpade aspekterna av statistisk inlärning men algoritmerna för statistisk inlärning st…</t>
+          <t>9 meningar i ett stycke (1211 tecken): I kursen ingår att hitta offentlig statistik samt att beskriva data med hjälp av olika grafer och att dra slutsatser om …</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>AMI22Z</t>
+          <t>AMI22T</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (464 tecken): Kursen är teoretisk och innehåller sannolikhetsteorins och statistiken grunder. Den omfattar slumpvariabler och dess för…</t>
+          <t>5 meningar i ett stycke (872 tecken): Kursen fokuserar främst på de tillämpade aspekterna av statistisk inlärning men algoritmerna för statistisk inlärning st…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>AMI22Z</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (662 tecken): Kursen behandlar linjärprogrammeringsproblem som är beräkningsmässigt möjliga att lösa och hur man empiriskt kan skatta …</t>
+          <t>6 meningar i ett stycke (464 tecken): Kursen är teoretisk och innehåller sannolikhetsteorins och statistiken grunder. Den omfattar slumpvariabler och dess för…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>AMI23J</t>
+          <t>AMI23C</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (607 tecken): Kursen innehåller arbetsplatsförlagt arbete vid en organisation vars verksamhet knyter an till studentens huvudområde so…</t>
+          <t>4 meningar i ett stycke (662 tecken): Kursen behandlar linjärprogrammeringsproblem som är beräkningsmässigt möjliga att lösa och hur man empiriskt kan skatta …</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>AMI23J</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (649 tecken): Kursen startar med en introduktion till GIS (Geografiska Informationssystem) och huvudsakliga karaktäristiska för rumsli…</t>
+          <t>4 meningar i ett stycke (607 tecken): Kursen innehåller arbetsplatsförlagt arbete vid en organisation vars verksamhet knyter an till studentens huvudområde so…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AMI295</t>
+          <t>AMI23L</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (684 tecken): Kursen ger en introduktion till Business Intelligence, analys och beslutsstöd. Den visar hur problem i företag kan lösas…</t>
+          <t>6 meningar i ett stycke (649 tecken): Kursen startar med en introduktion till GIS (Geografiska Informationssystem) och huvudsakliga karaktäristiska för rumsli…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>AMI295</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (609 tecken): I kursen studeras algebraiska system som inkluderar modulär aritmetik och polynomaritmetik. Logik och mängdlära behandla…</t>
+          <t>8 meningar i ett stycke (684 tecken): Kursen ger en introduktion till Business Intelligence, analys och beslutsstöd. Den visar hur problem i företag kan lösas…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,44 +3835,71 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>13 meningar i ett stycke (1224 tecken): Kursen börjar med en historisk och vetenskapligt introduktion till kryptografi, Kerchoffs princip och det grundläggande …</t>
+          <t>4 meningar i ett stycke (609 tecken): I kursen studeras algebraiska system som inkluderar modulär aritmetik och polynomaritmetik. Logik och mängdlära behandla…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>GMI26H</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>13 meningar i ett stycke (1224 tecken): Kursen börjar med en historisk och vetenskapligt introduktion till kryptografi, Kerchoffs princip och det grundläggande …</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
           <t>GMI35R</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ostyckad textmassa</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>7 meningar i ett stycke (768 tecken): Kursen ger en introduktion till hur operativsystem är uppbyggda och fungerar. Både teoretiska och praktiska aspekter av …</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI35R</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E127"/>
+  <autoFilter ref="A1:E128"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4126,6 +4153,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
